--- a/output/mariners_report_20260623.xlsx
+++ b/output/mariners_report_20260623.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statcast" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats to Improve" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Moves" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Targets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5295,6 +5296,811 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MLB TRADE &amp; WAIVER TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1B/DH TARGETS — xwOBA .330+, Barrel% 8%+, non-contender</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>xwOBA</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Barrel%</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>HardHit%</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>Yordan Alvarez</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C4" s="39" t="n">
+        <v>343</v>
+      </c>
+      <c r="D4" s="40" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F4" s="41" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G4" s="39" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" s="40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>Francisco Alvarez</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C5" s="39" t="n">
+        <v>166</v>
+      </c>
+      <c r="D5" s="40" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="E5" s="41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F5" s="41" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="I5" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C6" s="39" t="n">
+        <v>367</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" s="41" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="I6" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>Mike Trout</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>335</v>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="E7" s="41" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F7" s="41" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G7" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="I7" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Drake Baldwin</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>242</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="E8" s="41" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F8" s="41" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G8" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="40" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="I8" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>Taylor Ward</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>364</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F9" s="41" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="G9" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="40" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="I9" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>Aaron Judge</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C10" s="39" t="n">
+        <v>261</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F10" s="41" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="I10" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>Shohei Ohtani</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>330</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="I11" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Bryce Harper</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>324</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="E12" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="41" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>Juan Soto</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>257</v>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="E13" s="41" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="I13" s="38" t="inlineStr">
+        <is>
+          <t>1B/DH upgrade candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BULLPEN TARGETS — xwOBA against ≤.310, 20+ IP, non-contender</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>ERA</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>WHIP</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>K%</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>xwOBA vs</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>Dylan Lee</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="41" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F17" s="40" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G17" s="41" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="I17" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>Louis Varland</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="39" t="n">
+        <v>38</v>
+      </c>
+      <c r="D18" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G18" s="41" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="I18" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>Gus Varland</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" s="41" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E19" s="46" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="F19" s="40" t="n">
+        <v>1.685</v>
+      </c>
+      <c r="G19" s="41" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="I19" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>Rico Garcia</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="39" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" s="41" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E20" s="46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F20" s="40" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="G20" s="41" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H20" s="40" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="I20" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>Raisel Iglesias</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="39" t="n">
+        <v>23</v>
+      </c>
+      <c r="D21" s="41" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E21" s="46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F21" s="40" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="G21" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="H21" s="40" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="I21" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>Rico Garcia</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C22" s="39" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="G22" s="41" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H22" s="40" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="I22" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>Juan Morillo</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="39" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G23" s="41" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H23" s="40" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="I23" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Evan Sisk</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="39" t="n">
+        <v>29</v>
+      </c>
+      <c r="D24" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="E24" s="46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F24" s="40" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="G24" s="41" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="H24" s="40" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="I24" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="37" t="inlineStr">
+        <is>
+          <t>Taylor Rogers</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="39" t="n">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="E25" s="46" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="F25" s="40" t="n">
+        <v>1.517</v>
+      </c>
+      <c r="G25" s="41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H25" s="40" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="I25" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>Tyler Rogers</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="39" t="n">
+        <v>38</v>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F26" s="40" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="G26" s="41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H26" s="40" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="I26" s="38" t="inlineStr">
+        <is>
+          <t>Bullpen depth candidate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A15:I15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
